--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -762,7 +762,7 @@
     <t>158</t>
   </si>
   <si>
-    <t>Urgences psychiatriques 24h/24 7j/7</t>
+    <t>Urgences psychiatriques hospitalières</t>
   </si>
   <si>
     <t>159</t>
@@ -2178,7 +2178,7 @@
     <t>414</t>
   </si>
   <si>
-    <t>Soins de support en oncologie et hématologie</t>
+    <t>Soins de support</t>
   </si>
   <si>
     <t>416</t>
